--- a/backend/data/metadata_cer.xlsx
+++ b/backend/data/metadata_cer.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1433,7 +1433,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Verificar coupon_rate y coupon_frequency contra prospecto. | issue_date corregida por canje: original=2022-09-07, efectiva=2022-09-07</t>
+          <t>FechaEmision corregida: canje voluntario 2023. CER base efectiva 2023-08-01 (implica idx~6.77 = paridad~101%). Coupon 2% semiannual verificado BYMA.</t>
         </is>
       </c>
     </row>
@@ -1819,6 +1819,171 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>COMPLETAR amortization_schedule con las fechas y % de cada cuota. Fuente: prospecto oficial en CNV/Secretaría de Finanzas. Verificar coupon_rate y coupon_frequency contra prospecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TZXM8</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BONCER_ZC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2028-03-31</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>business_days_before:10</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>business_days_before:10</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>100</v>
+      </c>
+      <c r="J27" t="n">
+        <v>100</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>ZC, misma licitacion que TZXS8/TZXM9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TXM8</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BONCER_ZC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2028-06-30</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>business_days_before:10</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>business_days_before:10</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>100</v>
+      </c>
+      <c r="J28" t="n">
+        <v>100</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ZC estimado: duration=maturity benchmark. FechaEmision aprox. Verificar BYMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TXM9</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BONCER_ZC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2029-06-29</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>business_days_before:10</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>business_days_before:10</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>100</v>
+      </c>
+      <c r="J29" t="n">
+        <v>100</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ZC estimado: duration=maturity benchmark. FechaEmision aprox. Verificar BYMA.</t>
         </is>
       </c>
     </row>
